--- a/downloads/samples/CTC_Partner_Map_SAMPLE.xlsx
+++ b/downloads/samples/CTC_Partner_Map_SAMPLE.xlsx
@@ -541,7 +541,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>TIER 1  (9)   Approach in the first 30 days. Can host or co-host now.</t>
+          <t>TIER 1  (9)   First wave. Can host or co-host now.</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>TIER 2  (4)   Approach at 60 to 90 days. Wants a warm intro or a track record first.</t>
+          <t>TIER 2  (4)   Second wave. Wants a warm intro or a track record first.</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>TIER 3  (2)   Later. Real, but not a first-quarter target.</t>
+          <t>TIER 3  (2)   Later. Real, but slow, large, or out of reach for now.</t>
         </is>
       </c>
     </row>
